--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -759,39 +757,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -825,24 +821,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -975,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1127,9 +1123,9 @@
       <c r="I9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1266,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1275,24 +1271,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1309,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1386,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1425,11 +1421,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1569,17 +1565,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1609,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1716,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1725,24 +1721,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1759,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1875,11 +1871,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1909,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1935,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1947,8 +1943,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1957,37 +1955,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2093,47 +2093,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2167,11 +2171,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2201,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2231,7 +2235,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2239,8 +2243,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2249,37 +2255,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2313,11 +2321,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2347,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2377,7 +2385,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2385,10 +2393,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2397,39 +2403,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2463,11 +2467,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2497,12 +2501,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2527,7 +2531,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2535,51 +2539,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2613,11 +2613,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2647,12 +2647,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2685,10 +2685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2697,39 +2695,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2763,11 +2759,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2797,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2874,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2913,11 +2909,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2947,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3024,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3063,11 +3059,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3097,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3174,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3213,11 +3209,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3235,7 +3231,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3247,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3324,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3363,11 +3359,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3397,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3474,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3513,11 +3509,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3547,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3624,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3663,11 +3659,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3685,7 +3681,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3697,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3774,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3813,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3847,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,7 +3873,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3885,8 +3881,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3895,37 +3893,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>3</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4031,47 +4031,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4105,11 +4109,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4139,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,7 +4173,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4177,8 +4181,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>1</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4187,37 +4193,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4251,11 +4259,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4285,12 +4293,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4326,9 +4334,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4358,12 +4366,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4397,11 +4405,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4431,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4464,17 +4472,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4504,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4543,11 +4551,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4577,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4607,33 +4615,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4650,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4689,11 +4697,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4723,12 +4731,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4753,7 +4761,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4762,24 +4770,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4796,12 +4804,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4829,17 +4837,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4869,12 +4877,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4899,59 +4907,55 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4976,7 +4980,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4985,24 +4989,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5019,12 +5023,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5049,59 +5053,55 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5135,11 +5135,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5207,10 +5207,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5219,39 +5217,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5279,17 +5275,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5307,7 +5303,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5319,12 +5315,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5396,12 +5392,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5426,38 +5422,38 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5469,12 +5465,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5499,7 +5495,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5507,8 +5503,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5517,37 +5515,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5581,24 +5581,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5653,47 +5653,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5727,11 +5731,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5749,7 +5753,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5761,12 +5765,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5791,7 +5795,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5799,8 +5803,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5809,37 +5815,39 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5867,17 +5875,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5895,7 +5903,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5907,12 +5915,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5948,9 +5956,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5980,12 +5988,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6010,7 +6018,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6019,24 +6027,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6053,12 +6061,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6092,11 +6100,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6126,12 +6134,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6165,11 +6173,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6196,8 +6204,446 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,14 +636,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +759,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -823,9 +827,9 @@
       <c r="I5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -885,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,10 +897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -905,41 +907,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1115,17 +1115,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,14 +1232,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1262,33 +1262,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1421,24 +1421,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,14 +1532,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1565,17 +1565,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1712,33 +1712,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1871,24 +1871,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,14 +1982,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,14 +2132,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2171,11 +2171,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,14 +2282,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2321,11 +2321,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2355,14 +2355,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2393,8 +2393,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2403,39 +2405,41 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2467,11 +2471,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2501,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2542,9 +2546,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2574,14 +2578,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2613,11 +2617,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2647,14 +2651,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2686,11 +2690,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2720,14 +2724,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2759,11 +2763,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2793,14 +2797,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2831,10 +2835,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2843,41 +2845,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2909,11 +2909,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3020,14 +3020,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3059,11 +3059,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3170,14 +3170,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3209,11 +3209,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3320,14 +3320,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3359,11 +3359,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3470,14 +3470,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3509,11 +3509,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3620,14 +3620,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3659,11 +3659,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3770,14 +3770,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3920,14 +3920,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4070,14 +4070,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,9 +4261,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4293,14 +4293,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4331,8 +4331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4341,39 +4343,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4405,11 +4409,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4439,12 +4443,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,9 +4484,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,14 +4516,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4551,11 +4555,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4585,14 +4589,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4624,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4658,14 +4662,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4697,11 +4701,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4731,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4770,11 +4774,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4804,14 +4808,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4843,11 +4847,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4877,14 +4881,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4910,17 +4914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4950,14 +4954,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4989,11 +4993,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5023,14 +5027,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5053,33 +5057,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5096,14 +5100,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5135,11 +5139,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5169,14 +5173,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5199,33 +5203,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5242,14 +5246,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5275,17 +5279,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5315,14 +5319,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5345,7 +5349,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5353,10 +5357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5365,41 +5367,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5422,33 +5422,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5542,14 +5542,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5581,24 +5581,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5692,14 +5692,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5842,14 +5842,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5875,17 +5875,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5915,14 +5915,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5953,8 +5953,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5963,39 +5965,41 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6018,38 +6022,38 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -6061,12 +6065,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6102,9 +6106,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6134,14 +6138,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6164,7 +6168,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6173,24 +6177,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6207,14 +6211,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6246,11 +6250,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6280,14 +6284,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6319,11 +6323,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6353,14 +6357,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6392,11 +6396,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6426,14 +6430,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6465,11 +6469,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6499,14 +6503,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6538,11 +6542,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6572,14 +6576,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6611,11 +6615,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6642,8 +6646,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,8 +897,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -907,37 +909,39 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +966,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -971,24 +975,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1121,11 +1125,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1155,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,17 +1269,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1305,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1343,10 +1347,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1355,39 +1357,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1421,24 +1421,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1723,9 +1723,9 @@
       <c r="I17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1871,24 +1871,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2165,17 +2165,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2321,24 +2321,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2471,11 +2471,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2543,8 +2543,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2553,37 +2555,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2617,11 +2621,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2651,12 +2655,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2681,7 +2685,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2689,47 +2693,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2763,11 +2771,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2797,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2827,7 +2835,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2835,8 +2843,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>1</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2845,37 +2855,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2909,11 +2921,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2943,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2973,7 +2985,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2981,10 +2993,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2993,39 +3003,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3059,11 +3067,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3093,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3123,7 +3131,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3131,51 +3139,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3209,11 +3213,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3243,12 +3247,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3281,10 +3285,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3293,39 +3295,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3359,11 +3359,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3509,11 +3509,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3659,11 +3659,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4109,11 +4109,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4259,11 +4259,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4409,11 +4409,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4481,8 +4481,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4491,37 +4493,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4555,11 +4559,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>3</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4589,12 +4593,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4619,7 +4623,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4627,47 +4631,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4701,11 +4709,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4735,12 +4743,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4765,7 +4773,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4773,8 +4781,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>1</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4783,37 +4793,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4847,11 +4859,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4881,12 +4893,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4922,9 +4934,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4954,12 +4966,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4993,11 +5005,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5027,12 +5039,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5060,17 +5072,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5100,12 +5112,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5139,11 +5151,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5173,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5203,33 +5215,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5246,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5285,11 +5297,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5319,12 +5331,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5349,7 +5361,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5358,24 +5370,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5392,12 +5404,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5425,17 +5437,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5465,12 +5477,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5495,59 +5507,55 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5572,7 +5580,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5581,24 +5589,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5615,12 +5623,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5645,59 +5653,55 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5731,11 +5735,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5765,12 +5769,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5795,7 +5799,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5803,10 +5807,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5815,39 +5817,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5875,17 +5875,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6022,38 +6022,38 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6103,8 +6103,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6113,37 +6115,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6168,7 +6172,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6177,24 +6181,24 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6211,12 +6215,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6241,7 +6245,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6249,47 +6253,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6323,11 +6331,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6345,7 +6353,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6357,12 +6365,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6387,7 +6395,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6395,8 +6403,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6405,37 +6415,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6463,17 +6475,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6491,7 +6503,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6503,12 +6515,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6544,9 +6556,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,12 +6588,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6606,7 +6618,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6615,24 +6627,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6649,12 +6661,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6688,11 +6700,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6722,12 +6734,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6761,11 +6773,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6792,8 +6804,446 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -816,33 +816,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1269,17 +1269,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1347,8 +1347,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1357,37 +1359,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1421,24 +1425,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1571,11 +1575,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1605,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1715,17 +1719,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,10 +1797,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1805,39 +1807,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1871,24 +1871,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2173,9 +2173,9 @@
       <c r="I23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2321,24 +2321,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2471,11 +2471,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2615,17 +2615,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2771,24 +2771,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2921,11 +2921,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2993,8 +2993,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3003,37 +3005,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3067,11 +3071,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3101,12 +3105,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3131,7 +3135,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3139,47 +3143,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3213,11 +3221,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3247,12 +3255,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3277,7 +3285,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3285,8 +3293,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3295,37 +3305,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3359,11 +3371,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>10</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3393,12 +3405,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3423,7 +3435,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3431,10 +3443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3443,39 +3453,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3509,11 +3517,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3543,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3573,7 +3581,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3581,51 +3589,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3659,11 +3663,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3693,12 +3697,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3723,7 +3727,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3731,10 +3735,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3743,39 +3745,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4109,11 +4109,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4259,11 +4259,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4409,11 +4409,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4709,11 +4709,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4859,11 +4859,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4931,8 +4931,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4941,37 +4943,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5005,11 +5009,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5039,12 +5043,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5069,7 +5073,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5077,47 +5081,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5151,11 +5159,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5185,12 +5193,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,7 +5223,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5223,8 +5231,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5233,37 +5243,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5297,11 +5309,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5331,12 +5343,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5372,9 +5384,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5404,12 +5416,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5443,11 +5455,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5477,12 +5489,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5510,17 +5522,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5550,12 +5562,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5589,11 +5601,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5623,12 +5635,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5653,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5696,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5735,11 +5747,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5769,12 +5781,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5799,7 +5811,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5808,24 +5820,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5842,12 +5854,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5875,17 +5887,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5915,12 +5927,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5945,59 +5957,55 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6022,7 +6030,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6031,24 +6039,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6065,12 +6073,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6095,59 +6103,55 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6181,11 +6185,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6215,12 +6219,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6245,7 +6249,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6253,10 +6257,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6265,39 +6267,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6325,17 +6325,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6472,38 +6472,38 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6515,12 +6515,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6553,8 +6553,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6563,37 +6565,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6618,7 +6622,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6627,24 +6631,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6661,12 +6665,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6691,7 +6695,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6699,47 +6703,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6773,11 +6781,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6795,7 +6803,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6807,12 +6815,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6837,7 +6845,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6845,8 +6853,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>1</v>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6855,37 +6865,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6913,17 +6925,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6941,7 +6953,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6953,12 +6965,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6994,9 +7006,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7026,12 +7038,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7056,7 +7068,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7065,24 +7077,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7099,12 +7111,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7138,11 +7150,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7172,12 +7184,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7211,11 +7223,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7242,8 +7254,446 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -669,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -816,33 +812,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,14 +932,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -971,20 +967,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -992,7 +988,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1086,14 +1082,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1125,24 +1121,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,14 +1232,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1269,17 +1265,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1309,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1386,14 +1382,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1416,33 +1412,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1536,14 +1532,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1566,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1575,24 +1571,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1609,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1686,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1725,11 +1721,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1759,14 +1755,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1789,7 +1785,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,8 +1793,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1807,37 +1805,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1873,9 +1873,9 @@
       <c r="I19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1905,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1943,10 +1943,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1955,41 +1953,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2021,11 +2017,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2055,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,14 +2128,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2165,17 +2161,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2205,12 +2201,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,14 +2278,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2312,33 +2308,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2355,12 +2351,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2432,14 +2428,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2462,7 +2458,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2471,24 +2467,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2505,12 +2501,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2582,14 +2578,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2615,17 +2611,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2655,12 +2651,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2732,14 +2728,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2762,33 +2758,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2805,12 +2801,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2882,14 +2878,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2912,7 +2908,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2921,24 +2917,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2955,12 +2951,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3032,14 +3028,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3071,11 +3067,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3105,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3182,14 +3178,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3221,11 +3217,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3255,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3332,14 +3328,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3371,11 +3367,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3405,14 +3401,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3435,7 +3431,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3443,8 +3439,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3453,39 +3451,41 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3517,11 +3517,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3592,9 +3592,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3624,14 +3624,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3736,11 +3736,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3770,14 +3770,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3843,14 +3843,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3881,10 +3881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3893,41 +3891,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3959,11 +3955,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3993,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4070,14 +4066,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4109,11 +4105,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4143,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4220,14 +4216,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4259,11 +4255,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4293,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4370,14 +4366,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4409,11 +4405,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4443,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4520,14 +4516,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4559,11 +4555,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4593,12 +4589,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4670,14 +4666,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4709,11 +4705,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4731,7 +4727,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4743,12 +4739,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4820,14 +4816,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4859,11 +4855,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4881,7 +4877,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4893,12 +4889,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4970,14 +4966,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5009,11 +5005,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5043,12 +5039,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5120,14 +5116,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5159,7 +5155,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5193,12 +5189,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5270,12 +5266,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5311,9 +5307,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5343,14 +5339,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5373,7 +5369,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5381,8 +5377,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5391,39 +5389,41 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5455,11 +5455,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5530,9 +5530,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5562,14 +5562,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5601,11 +5601,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5635,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5674,11 +5674,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5708,14 +5708,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5747,11 +5747,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5781,14 +5781,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5820,11 +5820,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5854,14 +5854,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5893,11 +5893,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5927,14 +5927,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5960,17 +5960,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6000,14 +6000,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6073,14 +6073,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6103,33 +6103,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6146,14 +6146,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6185,11 +6185,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6219,14 +6219,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6249,33 +6249,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6292,14 +6292,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6325,17 +6325,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6365,14 +6365,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6403,10 +6403,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6415,41 +6413,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6472,33 +6468,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6515,12 +6511,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6592,14 +6588,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6622,7 +6618,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6631,24 +6627,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6665,12 +6661,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6742,14 +6738,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6781,7 +6777,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6803,7 +6799,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6815,12 +6811,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6892,14 +6888,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6925,17 +6921,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6965,14 +6961,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6995,7 +6991,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7003,8 +6999,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7013,39 +7011,41 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7068,38 +7068,38 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7152,9 +7152,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7184,14 +7184,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7223,24 +7223,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7257,14 +7257,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7296,11 +7296,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7330,14 +7330,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7369,11 +7369,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7403,14 +7403,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7442,11 +7442,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7476,14 +7476,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7515,11 +7515,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7549,14 +7549,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7588,11 +7588,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7622,14 +7622,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7661,11 +7661,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7692,8 +7692,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,51 +743,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -815,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,10 +889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -905,39 +899,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1005,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,33 +1104,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1155,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,33 +1254,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1305,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,33 +1404,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1455,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1532,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1554,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1571,24 +1563,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1605,12 +1597,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1674,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1715,17 +1707,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1755,12 +1747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1832,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1871,24 +1863,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1935,7 +1927,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1943,8 +1935,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1953,37 +1947,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2017,7 +2013,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2051,12 +2047,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2128,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2167,11 +2163,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2201,12 +2197,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2231,7 +2227,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2239,10 +2235,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2251,39 +2245,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2311,9 +2303,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2321,7 +2313,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2351,12 +2343,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2428,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2458,7 +2450,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2467,24 +2459,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 900,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2501,12 +2493,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2578,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2611,17 +2603,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2651,12 +2643,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2728,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2758,33 +2750,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2801,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2878,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2908,7 +2900,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2917,24 +2909,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2951,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3028,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3061,17 +3053,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>6</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3101,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3178,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3208,7 +3200,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3217,24 +3209,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3251,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3328,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3367,11 +3359,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3401,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3478,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3517,11 +3509,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3551,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3581,7 +3573,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3589,8 +3581,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3599,37 +3593,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3663,11 +3659,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 116,7%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3697,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3727,7 +3723,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3735,47 +3731,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3916,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4027,51 +4027,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4105,11 +4101,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4139,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,7 +4165,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4177,10 +4173,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4189,39 +4183,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4255,11 +4247,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4289,12 +4281,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4366,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4405,11 +4397,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4439,12 +4431,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4516,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4555,11 +4547,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4589,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4666,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4705,11 +4697,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4739,12 +4731,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4816,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4855,11 +4847,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4877,7 +4869,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4889,12 +4881,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4966,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5005,11 +4997,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5039,12 +5031,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5116,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5155,11 +5147,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5177,7 +5169,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5189,12 +5181,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5266,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5305,11 +5297,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5339,12 +5331,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5416,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5455,11 +5447,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5489,12 +5481,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5519,7 +5511,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5527,8 +5519,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5537,37 +5531,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5601,11 +5597,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5635,12 +5631,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5665,7 +5661,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5673,47 +5669,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5747,11 +5747,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5854,12 +5854,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5893,11 +5893,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6106,17 +6106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6185,11 +6185,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6249,33 +6249,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6331,11 +6331,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6395,33 +6395,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6471,17 +6471,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6541,59 +6541,55 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6618,7 +6614,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6627,24 +6623,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6661,12 +6657,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6691,7 +6687,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6699,10 +6695,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6711,39 +6705,37 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6771,17 +6763,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6811,12 +6803,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6888,12 +6880,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6918,7 +6910,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6929,27 +6921,27 @@
       <c r="I87" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6961,12 +6953,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7038,12 +7030,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7071,17 +7063,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7099,7 +7091,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -7111,12 +7103,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7141,7 +7133,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7149,8 +7141,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7159,37 +7153,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7214,7 +7210,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7223,29 +7219,29 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7257,12 +7253,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7287,7 +7283,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7295,47 +7291,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7363,17 +7363,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,6%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7476,12 +7476,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7515,24 +7515,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7661,11 +7661,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>20</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7807,11 +7807,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7838,8 +7838,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,47 +597,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +674,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,47 +751,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +829,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +902,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -924,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +975,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,51 +1047,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1107,17 +1115,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1147,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1185,10 +1193,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1197,39 +1203,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,55 +1258,59 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1374,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,47 +1420,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1524,12 +1536,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1554,7 +1566,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1562,47 +1574,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1674,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1704,55 +1720,59 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1824,12 +1844,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1854,7 +1874,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1862,47 +1882,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1974,12 +1998,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2004,7 +2028,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2012,47 +2036,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2077,7 +2105,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2085,10 +2113,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2097,39 +2123,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2163,11 +2187,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2197,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2238,9 +2262,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2270,12 +2294,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2303,17 +2327,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2343,12 +2367,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2373,7 +2397,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2381,51 +2405,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2450,7 +2470,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2459,24 +2479,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2493,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,7 +2543,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2531,51 +2551,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2603,17 +2619,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2643,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2673,7 +2689,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2681,10 +2697,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2693,39 +2707,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2750,7 +2762,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2759,24 +2771,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2793,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2870,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2903,17 +2915,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2943,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3020,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3050,33 +3062,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3093,12 +3105,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3170,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3200,7 +3212,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3209,16 +3221,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>5</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3243,12 +3255,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3320,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3359,11 +3371,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3393,12 +3405,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3470,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3503,17 +3515,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3543,12 +3555,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3620,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3650,7 +3662,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3659,24 +3671,24 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3693,12 +3705,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3770,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3809,11 +3821,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3843,12 +3855,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3873,7 +3885,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3881,8 +3893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3891,37 +3905,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3955,11 +3971,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3989,12 +4005,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4030,9 +4046,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4078,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4135,12 +4151,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4165,7 +4181,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4173,8 +4189,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>1</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4183,37 +4201,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4251,7 +4271,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4281,12 +4301,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4358,12 +4378,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,17 +4411,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4431,12 +4451,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4508,12 +4528,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4538,7 +4558,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4547,24 +4567,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4581,12 +4601,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4658,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4697,11 +4717,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4731,12 +4751,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4808,12 +4828,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4841,17 +4861,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4881,12 +4901,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4958,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4988,7 +5008,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4997,24 +5017,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5031,12 +5051,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5108,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5147,11 +5167,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5169,7 +5189,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5181,12 +5201,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5258,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5297,11 +5317,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5331,12 +5351,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5408,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5447,11 +5467,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5481,12 +5501,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5558,12 +5578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5597,11 +5617,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5631,12 +5651,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5661,7 +5681,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5669,10 +5689,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5681,39 +5699,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5747,11 +5763,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5781,12 +5797,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5822,9 +5838,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5854,12 +5870,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5893,11 +5909,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5927,12 +5943,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5966,11 +5982,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6000,12 +6016,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6043,7 +6059,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6073,12 +6089,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6103,7 +6119,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6111,8 +6127,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>1</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6121,37 +6139,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6185,11 +6205,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6219,12 +6239,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6249,7 +6269,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6257,47 +6277,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6331,11 +6355,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6365,12 +6389,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6395,55 +6419,59 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6477,11 +6505,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6511,12 +6539,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6541,55 +6569,59 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6623,11 +6655,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6657,12 +6689,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6687,7 +6719,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6695,8 +6727,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>9</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6705,37 +6739,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6763,17 +6799,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6803,12 +6839,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6880,12 +6916,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6910,7 +6946,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6919,29 +6955,29 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6953,12 +6989,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7030,12 +7066,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7069,11 +7105,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7103,12 +7139,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7180,12 +7216,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7219,11 +7255,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7241,7 +7277,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7253,12 +7289,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7330,12 +7366,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7363,17 +7399,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7391,7 +7427,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -7403,12 +7439,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7433,7 +7469,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7441,8 +7477,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7451,37 +7489,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7506,7 +7546,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7515,24 +7555,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7549,12 +7589,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7590,9 +7630,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7622,12 +7662,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7661,11 +7701,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7695,12 +7735,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7734,11 +7774,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7768,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7807,11 +7847,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7841,12 +7881,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7880,11 +7920,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7914,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7953,11 +7993,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7987,12 +8027,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8026,11 +8066,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8060,12 +8100,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8099,11 +8139,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8130,8 +8170,1776 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,59 +589,55 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -666,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,59 +735,55 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -829,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -863,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -893,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -902,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -936,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -975,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1009,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1121,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1155,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1188,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1343,51 +1327,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,59 +1392,55 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1497,10 +1473,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1509,39 +1483,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1566,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1574,51 +1546,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1690,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1720,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1728,51 +1696,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1844,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1874,7 +1838,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1882,51 +1846,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1998,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2028,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2036,51 +1996,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2105,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2113,8 +2069,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2123,37 +2081,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2187,11 +2147,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,8%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2221,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2251,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2259,47 +2219,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2327,17 +2291,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2367,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2397,7 +2361,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2405,47 +2369,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2470,7 +2438,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2479,24 +2447,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2513,12 +2481,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2543,7 +2511,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2551,47 +2519,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2625,11 +2597,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2659,12 +2631,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,7 +2661,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2697,8 +2669,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>1</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2707,37 +2681,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2762,7 +2738,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2770,47 +2746,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2882,12 +2862,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2912,55 +2892,59 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3032,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3062,55 +3046,59 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3182,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3212,7 +3200,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3220,47 +3208,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3332,12 +3324,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3362,7 +3354,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3370,47 +3362,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3482,12 +3478,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3512,55 +3508,59 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3670,47 +3670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3782,12 +3786,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3812,7 +3816,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3820,47 +3824,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3932,12 +3940,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3971,11 +3979,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -4005,12 +4013,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4078,12 +4086,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4117,11 +4125,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4151,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4181,7 +4189,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4189,51 +4197,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4267,11 +4271,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4301,12 +4305,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4331,7 +4335,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4339,10 +4343,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4351,39 +4353,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4408,55 +4408,59 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4528,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4558,7 +4562,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4566,47 +4570,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4678,12 +4686,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4708,7 +4716,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4716,47 +4724,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4828,12 +4840,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4858,55 +4870,59 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4978,12 +4994,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5008,7 +5024,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5016,47 +5032,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5128,12 +5148,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5158,7 +5178,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5166,47 +5186,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5231,7 +5255,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5239,10 +5263,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5251,39 +5273,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5317,11 +5337,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5351,12 +5371,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5381,7 +5401,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5389,51 +5409,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5461,17 +5477,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5501,12 +5517,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5531,7 +5547,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5539,51 +5555,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5608,7 +5620,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5617,24 +5629,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5651,12 +5663,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5690,11 +5702,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5724,12 +5736,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5763,11 +5775,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 116,7%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5797,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5836,11 +5848,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5870,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5909,11 +5921,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5943,12 +5955,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5973,7 +5985,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5981,8 +5993,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5991,37 +6005,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6049,17 +6065,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6089,12 +6105,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6166,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6196,12 +6212,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
@@ -6209,20 +6225,20 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6239,12 +6255,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6316,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6346,7 +6362,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6355,24 +6371,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6389,12 +6405,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6466,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6505,11 +6521,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6539,12 +6555,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6616,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6649,17 +6665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6689,12 +6705,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6766,12 +6782,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6796,7 +6812,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6805,24 +6821,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6839,12 +6855,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6916,12 +6932,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6955,11 +6971,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6977,7 +6993,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6989,12 +7005,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7066,12 +7082,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7105,11 +7121,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7139,12 +7155,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7169,7 +7185,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7177,10 +7193,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7189,39 +7203,37 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7255,11 +7267,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7289,12 +7301,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7366,12 +7378,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7405,11 +7417,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7439,12 +7451,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7516,12 +7528,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7549,17 +7561,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7589,12 +7601,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7619,7 +7631,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7627,8 +7639,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7637,37 +7651,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7692,7 +7708,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7701,24 +7717,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7735,12 +7751,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7765,7 +7781,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7773,47 +7789,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7847,11 +7867,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7881,12 +7901,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7911,7 +7931,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7919,8 +7939,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>1</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7929,37 +7951,39 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7987,17 +8011,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8027,12 +8051,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8057,7 +8081,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8065,47 +8089,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8130,7 +8158,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8139,24 +8167,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8173,12 +8201,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8203,55 +8231,59 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8285,11 +8317,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8319,12 +8351,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8349,55 +8381,59 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8431,11 +8467,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8465,12 +8501,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8495,7 +8531,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8503,8 +8539,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>9</v>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8513,37 +8551,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8571,17 +8611,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8611,12 +8651,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8688,12 +8728,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8718,7 +8758,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8727,24 +8767,24 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8761,12 +8801,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8791,7 +8831,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8799,10 +8839,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8811,39 +8849,37 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8877,11 +8913,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8911,12 +8947,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8941,7 +8977,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8949,51 +8985,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9027,11 +9059,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9049,7 +9081,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -9061,12 +9093,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9091,7 +9123,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9099,10 +9131,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9111,39 +9141,37 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9171,17 +9199,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9199,7 +9227,7 @@
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
@@ -9211,12 +9239,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9241,7 +9269,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9249,8 +9277,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9259,37 +9289,39 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9314,7 +9346,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9323,24 +9355,24 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9357,12 +9389,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9387,7 +9419,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9395,47 +9427,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9469,11 +9505,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9503,12 +9539,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9533,7 +9569,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9541,8 +9577,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>1</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9551,37 +9589,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9615,11 +9655,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9649,12 +9689,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9679,7 +9719,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9687,47 +9727,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9761,11 +9805,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>4</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9795,12 +9839,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9825,7 +9869,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9833,8 +9877,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>1</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9843,37 +9889,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9907,11 +9955,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9938,8 +9986,3110 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 52,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 36,4%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -886,20 +886,20 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 77,8%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1619,10 +1619,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1631,41 +1629,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1697,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1808,14 +1804,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1847,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1881,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1958,14 +1954,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1997,11 +1993,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2108,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2147,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,8%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2258,14 +2254,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2297,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 53,8%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2331,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2408,14 +2404,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2447,11 +2443,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2481,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2558,14 +2554,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2597,11 +2593,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2631,12 +2627,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2708,14 +2704,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2738,7 +2734,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2746,10 +2742,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2758,39 +2752,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2862,12 +2854,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2939,12 +2931,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3016,12 +3008,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,12 +3085,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3170,12 +3162,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,12 +3239,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3324,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3401,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3478,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3555,12 +3547,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3632,12 +3624,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3786,12 +3778,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3863,12 +3855,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3940,14 +3932,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3970,7 +3962,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3978,8 +3970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3988,39 +3982,41 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4043,7 +4039,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4051,8 +4047,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4061,37 +4059,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4127,9 +4127,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4200,9 +4200,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4232,14 +4232,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4271,11 +4271,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4305,14 +4305,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4344,11 +4344,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4378,14 +4378,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4416,10 +4416,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4428,41 +4426,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4485,7 +4481,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4493,10 +4489,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4505,39 +4499,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4601,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4686,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4763,12 +4755,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4840,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4917,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4994,12 +4986,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5071,12 +5063,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5148,12 +5140,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5225,14 +5217,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5255,7 +5247,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5263,8 +5255,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5273,39 +5267,41 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5328,7 +5324,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5336,8 +5332,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5346,37 +5344,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5412,9 +5412,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5444,14 +5444,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5477,17 +5477,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5517,14 +5517,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5556,11 +5556,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5590,14 +5590,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5620,33 +5620,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5663,14 +5663,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5702,11 +5702,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5736,14 +5736,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5775,24 +5775,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5848,11 +5848,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5882,14 +5882,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5921,11 +5921,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5955,14 +5955,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5993,10 +5993,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6005,41 +6003,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6065,17 +6061,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▲ 71,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6105,12 +6101,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6182,14 +6178,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6212,33 +6208,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6255,12 +6251,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6332,14 +6328,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6367,20 +6363,20 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6388,7 +6384,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6405,12 +6401,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6482,14 +6478,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6512,7 +6508,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6521,24 +6517,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6555,12 +6551,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6632,14 +6628,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6665,17 +6661,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6705,12 +6701,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6782,14 +6778,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6812,33 +6808,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6855,12 +6851,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6932,14 +6928,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6962,7 +6958,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6971,24 +6967,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7005,12 +7001,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7082,14 +7078,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7121,11 +7117,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7155,14 +7151,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7185,7 +7181,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7193,8 +7189,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7203,37 +7201,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7269,9 +7269,9 @@
       <c r="I91" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7301,14 +7301,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7339,10 +7339,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7351,41 +7349,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7417,11 +7413,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7451,12 +7447,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7528,14 +7524,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7561,17 +7557,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7601,12 +7597,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7678,14 +7674,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7708,33 +7704,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▲ 900,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7751,12 +7747,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7828,14 +7824,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7858,7 +7854,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7867,24 +7863,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7901,12 +7897,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7978,14 +7974,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8011,17 +8007,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8051,12 +8047,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8128,14 +8124,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8158,33 +8154,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8201,12 +8197,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8278,14 +8274,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8308,7 +8304,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8317,24 +8313,24 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>3</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8351,12 +8347,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8428,14 +8424,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8467,11 +8463,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8501,12 +8497,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8578,14 +8574,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8617,11 +8613,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8651,12 +8647,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8728,14 +8724,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8767,11 +8763,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8801,14 +8797,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8831,7 +8827,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8839,8 +8835,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8849,39 +8847,41 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8913,11 +8913,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▲ 116,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8988,9 +8988,9 @@
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9020,14 +9020,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9059,11 +9059,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9093,14 +9093,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9132,11 +9132,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9166,14 +9166,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9205,11 +9205,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9239,14 +9239,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9277,10 +9277,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9289,41 +9287,39 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9355,11 +9351,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9389,12 +9385,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9466,14 +9462,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9505,11 +9501,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9539,12 +9535,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9616,14 +9612,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9655,11 +9651,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9689,12 +9685,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9766,14 +9762,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9805,11 +9801,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9839,12 +9835,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9916,14 +9912,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9955,11 +9951,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9989,12 +9985,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10066,14 +10062,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10105,11 +10101,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10127,7 +10123,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -10139,12 +10135,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10216,14 +10212,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10255,11 +10251,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10277,7 +10273,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10289,12 +10285,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10366,14 +10362,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10405,11 +10401,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10439,12 +10435,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10516,14 +10512,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10555,7 +10551,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10589,12 +10585,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10666,12 +10662,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10707,9 +10703,9 @@
       <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10739,14 +10735,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10769,7 +10765,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10777,8 +10773,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10787,39 +10785,41 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10851,11 +10851,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10926,9 +10926,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10958,14 +10958,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10997,11 +10997,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11031,14 +11031,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11070,11 +11070,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11104,14 +11104,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11143,11 +11143,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11177,14 +11177,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11216,11 +11216,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,14 +11250,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11289,11 +11289,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11323,14 +11323,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11356,17 +11356,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11396,14 +11396,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11435,11 +11435,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11469,14 +11469,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11499,33 +11499,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11542,14 +11542,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11581,11 +11581,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11615,14 +11615,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11645,33 +11645,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11688,14 +11688,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11721,17 +11721,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11761,14 +11761,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11799,10 +11799,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11811,41 +11809,39 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11868,33 +11864,33 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11911,12 +11907,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11988,14 +11984,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12018,7 +12014,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12027,24 +12023,24 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -12061,12 +12057,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12138,14 +12134,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12177,9 +12173,9 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -12199,7 +12195,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -12211,12 +12207,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12288,14 +12284,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12321,17 +12317,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12361,14 +12357,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12391,7 +12387,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12399,8 +12395,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="2" t="n">
-        <v>0</v>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -12409,39 +12407,41 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12464,38 +12464,38 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12548,9 +12548,9 @@
       <c r="I162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12580,14 +12580,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12619,24 +12619,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,6%</t>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12653,14 +12653,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12692,11 +12692,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12726,14 +12726,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12765,11 +12765,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12799,14 +12799,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12838,11 +12838,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12872,14 +12872,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12911,11 +12911,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>▼ 31,2%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12945,14 +12945,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12984,11 +12984,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13018,14 +13018,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13057,11 +13057,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13088,8 +13088,154 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
-        </is>
-      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1032,20 +1032,20 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1765,10 +1765,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1777,41 +1775,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1834,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1839,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1954,14 +1950,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1993,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2027,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2104,14 +2100,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2143,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2254,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2293,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,8%</t>
+        <v>9</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2404,14 +2400,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2443,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,8%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2477,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2554,14 +2550,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2593,11 +2589,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2627,12 +2623,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2704,14 +2700,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2743,11 +2739,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2777,12 +2773,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2854,14 +2850,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2884,7 +2880,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2892,10 +2888,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2904,39 +2898,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3008,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3085,12 +3077,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3162,12 +3154,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3239,12 +3231,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3316,12 +3308,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3393,12 +3385,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3470,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,12 +3539,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3624,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3701,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3778,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3855,12 +3847,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3932,12 +3924,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4001,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4086,14 +4078,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4116,7 +4108,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4124,8 +4116,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4134,39 +4128,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4189,7 +4185,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4197,8 +4193,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4207,37 +4205,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4273,9 +4273,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4346,9 +4346,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4378,14 +4378,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4417,11 +4417,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4451,14 +4451,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4524,14 +4524,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4562,10 +4562,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4574,41 +4572,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4631,7 +4627,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4639,10 +4635,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4651,39 +4645,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4755,12 +4747,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4832,12 +4824,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4901,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4986,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5063,12 +5055,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5140,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5217,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5294,12 +5286,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5371,14 +5363,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5401,7 +5393,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5409,8 +5401,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5419,39 +5413,41 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5474,7 +5470,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5482,8 +5478,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5492,37 +5490,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5558,9 +5558,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5590,14 +5590,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5623,17 +5623,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5663,14 +5663,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5702,11 +5702,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5736,14 +5736,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5766,33 +5766,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5848,11 +5848,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5882,14 +5882,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5921,24 +5921,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5955,14 +5955,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5994,11 +5994,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6028,14 +6028,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6067,11 +6067,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6101,14 +6101,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6139,10 +6139,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6151,41 +6149,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6211,17 +6207,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6251,12 +6247,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6328,14 +6324,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6358,33 +6354,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6401,12 +6397,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6478,14 +6474,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6513,20 +6509,20 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6534,7 +6530,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6551,12 +6547,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6628,14 +6624,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6658,7 +6654,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6667,24 +6663,24 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6701,12 +6697,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6778,14 +6774,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6811,17 +6807,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6851,12 +6847,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6928,14 +6924,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6958,33 +6954,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7001,12 +6997,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7078,14 +7074,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7108,7 +7104,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7117,24 +7113,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7151,12 +7147,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7228,14 +7224,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7267,11 +7263,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7301,14 +7297,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7331,7 +7327,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7339,8 +7335,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7349,37 +7347,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7415,9 +7415,9 @@
       <c r="I93" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7447,14 +7447,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7485,10 +7485,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7497,41 +7495,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7563,11 +7559,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7597,12 +7593,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7674,14 +7670,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7707,17 +7703,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7747,12 +7743,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7824,14 +7820,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7854,33 +7850,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7897,12 +7893,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7974,14 +7970,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8004,7 +8000,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8013,24 +8009,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8047,12 +8043,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8124,14 +8120,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8157,17 +8153,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8197,12 +8193,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8274,14 +8270,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8304,33 +8300,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8347,12 +8343,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8424,14 +8420,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8454,7 +8450,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8463,24 +8459,24 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8497,12 +8493,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8574,14 +8570,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8613,11 +8609,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8647,12 +8643,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8724,14 +8720,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8763,11 +8759,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8797,12 +8793,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8874,14 +8870,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8913,11 +8909,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8947,14 +8943,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8977,7 +8973,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8985,8 +8981,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8995,39 +8993,41 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9059,11 +9059,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9134,9 +9134,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9166,14 +9166,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9205,11 +9205,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9239,14 +9239,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9278,11 +9278,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9312,14 +9312,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9351,11 +9351,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9423,10 +9423,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -9435,41 +9433,39 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9501,11 +9497,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9535,12 +9531,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9612,14 +9608,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9651,11 +9647,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9685,12 +9681,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9762,14 +9758,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9801,11 +9797,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9835,12 +9831,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9912,14 +9908,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9951,11 +9947,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9985,12 +9981,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10062,14 +10058,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10101,11 +10097,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10135,12 +10131,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10212,14 +10208,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10251,11 +10247,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10273,7 +10269,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10285,12 +10281,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10362,14 +10358,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10401,11 +10397,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10423,7 +10419,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10435,12 +10431,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10512,14 +10508,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10551,11 +10547,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10585,12 +10581,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10662,14 +10658,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10701,7 +10697,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10735,12 +10731,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10812,12 +10808,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10853,9 +10849,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10885,14 +10881,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10915,7 +10911,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10923,8 +10919,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -10933,39 +10931,41 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10997,11 +10997,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11072,9 +11072,9 @@
       <c r="I142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11104,14 +11104,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11143,11 +11143,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11177,14 +11177,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11216,11 +11216,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,14 +11250,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11289,11 +11289,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11323,14 +11323,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11362,11 +11362,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11396,14 +11396,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11435,11 +11435,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11469,14 +11469,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11502,17 +11502,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11542,14 +11542,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11581,11 +11581,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11615,14 +11615,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11645,33 +11645,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11688,14 +11688,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11727,11 +11727,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11761,14 +11761,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11791,33 +11791,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11834,14 +11834,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11867,17 +11867,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11907,14 +11907,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11945,10 +11945,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I154" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -11957,41 +11955,39 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12014,33 +12010,33 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -12057,12 +12053,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12134,14 +12130,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12164,7 +12160,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12173,24 +12169,24 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12207,12 +12203,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12284,14 +12280,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12323,7 +12319,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -12345,7 +12341,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12357,12 +12353,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12434,14 +12430,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12467,17 +12463,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12507,14 +12503,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12537,7 +12533,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12545,8 +12541,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="2" t="n">
-        <v>0</v>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -12555,39 +12553,41 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12610,38 +12610,38 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12653,12 +12653,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12694,9 +12694,9 @@
       <c r="I164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12726,14 +12726,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12765,24 +12765,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12799,14 +12799,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12838,11 +12838,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12872,14 +12872,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12911,11 +12911,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12945,14 +12945,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12984,11 +12984,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13018,14 +13018,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13057,11 +13057,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13091,14 +13091,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13130,11 +13130,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13164,14 +13164,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13203,11 +13203,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13234,8 +13234,154 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>69</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 527,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 77,8%</t>
+        <v>4</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1687,17 +1687,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1911,10 +1911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1923,41 +1921,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2100,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2139,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2250,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2289,11 +2285,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2400,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2439,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,8%</t>
+        <v>9</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2550,14 +2546,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2589,11 +2585,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,8%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2623,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2700,14 +2696,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2739,11 +2735,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2773,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2850,14 +2846,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -2889,11 +2885,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2923,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3000,14 +2996,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -3030,7 +3026,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3038,10 +3034,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3050,39 +3044,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3154,12 +3146,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3231,12 +3223,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3308,12 +3300,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3385,12 +3377,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3462,12 +3454,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3539,12 +3531,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3616,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,12 +3685,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3770,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3924,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4001,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4078,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4155,12 +4147,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4232,14 +4224,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4262,7 +4254,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4270,8 +4262,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4280,39 +4274,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4335,7 +4331,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4343,8 +4339,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4353,37 +4351,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4419,9 +4419,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4492,9 +4492,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4524,14 +4524,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4563,11 +4563,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4597,14 +4597,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4636,11 +4636,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4670,14 +4670,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4708,10 +4708,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4720,41 +4718,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -4777,7 +4773,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4785,10 +4781,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4797,39 +4791,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4901,12 +4893,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4978,12 +4970,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5055,12 +5047,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5132,12 +5124,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5201,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5286,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5363,12 +5355,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5440,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5517,14 +5509,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5547,7 +5539,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5555,8 +5547,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5565,39 +5559,41 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5620,7 +5616,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5628,8 +5624,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5638,37 +5636,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5704,9 +5704,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5736,14 +5736,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5769,17 +5769,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5848,11 +5848,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5882,14 +5882,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5912,33 +5912,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5955,14 +5955,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -5994,11 +5994,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6028,14 +6028,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6067,24 +6067,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6101,14 +6101,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6140,11 +6140,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6174,14 +6174,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6213,11 +6213,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6247,14 +6247,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6285,10 +6285,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6297,41 +6295,39 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6357,17 +6353,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6397,12 +6393,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6474,14 +6470,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6504,33 +6500,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6547,12 +6543,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6624,14 +6620,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6659,20 +6655,20 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6680,7 +6676,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6697,12 +6693,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6774,14 +6770,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6804,7 +6800,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6813,24 +6809,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6847,12 +6843,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6924,14 +6920,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -6957,17 +6953,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6997,12 +6993,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7074,14 +7070,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7104,33 +7100,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7147,12 +7143,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7224,14 +7220,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7254,7 +7250,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7263,24 +7259,24 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7297,12 +7293,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7374,14 +7370,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7413,11 +7409,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7447,14 +7443,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7477,7 +7473,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7485,8 +7481,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7495,37 +7493,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7561,9 +7561,9 @@
       <c r="I95" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7593,14 +7593,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7631,10 +7631,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7643,41 +7641,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7709,11 +7705,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7743,12 +7739,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7820,14 +7816,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -7853,17 +7849,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7893,12 +7889,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7970,14 +7966,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8000,33 +7996,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8043,12 +8039,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8120,14 +8116,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8150,7 +8146,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8159,24 +8155,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8193,12 +8189,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8270,14 +8266,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8303,17 +8299,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8343,12 +8339,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8420,14 +8416,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8450,33 +8446,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>6</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8493,12 +8489,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8570,14 +8566,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8600,7 +8596,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8609,24 +8605,24 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8643,12 +8639,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8720,14 +8716,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8759,11 +8755,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8793,12 +8789,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8870,14 +8866,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -8909,11 +8905,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8943,12 +8939,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9020,14 +9016,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9059,11 +9055,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9093,14 +9089,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9123,7 +9119,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9131,8 +9127,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9141,39 +9139,41 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9205,11 +9205,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9280,9 +9280,9 @@
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9312,14 +9312,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9351,11 +9351,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9424,11 +9424,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9458,14 +9458,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9497,11 +9497,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9531,14 +9531,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9569,10 +9569,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9581,41 +9579,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9647,11 +9643,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9681,12 +9677,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9758,14 +9754,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9797,11 +9793,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9831,12 +9827,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9908,14 +9904,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -9947,11 +9943,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9981,12 +9977,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10058,14 +10054,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10097,11 +10093,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10131,12 +10127,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10208,14 +10204,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10247,11 +10243,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10281,12 +10277,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10358,14 +10354,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10397,11 +10393,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10419,7 +10415,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10431,12 +10427,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10508,14 +10504,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10547,11 +10543,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10569,7 +10565,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10581,12 +10577,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10658,14 +10654,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10697,11 +10693,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10731,12 +10727,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10808,14 +10804,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -10847,7 +10843,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10881,12 +10877,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10958,12 +10954,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10999,9 +10995,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11031,14 +11027,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11061,7 +11057,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11069,8 +11065,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>0</v>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -11079,39 +11077,41 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11143,11 +11143,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11177,12 +11177,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11218,9 +11218,9 @@
       <c r="I144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,14 +11250,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11289,11 +11289,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11323,14 +11323,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11362,11 +11362,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11396,14 +11396,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11435,11 +11435,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11469,14 +11469,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11508,11 +11508,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11542,14 +11542,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11581,11 +11581,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11615,14 +11615,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11648,17 +11648,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11688,14 +11688,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11727,11 +11727,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11761,14 +11761,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11791,33 +11791,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11834,14 +11834,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11873,11 +11873,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11907,14 +11907,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -11937,33 +11937,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11980,14 +11980,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12013,17 +12013,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12053,14 +12053,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12091,10 +12091,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I156" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12103,41 +12101,39 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12160,33 +12156,33 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12203,12 +12199,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12280,14 +12276,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12310,7 +12306,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12319,24 +12315,24 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12353,12 +12349,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12430,14 +12426,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12469,7 +12465,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -12491,7 +12487,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12503,12 +12499,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12580,14 +12576,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12613,17 +12609,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12653,14 +12649,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12683,7 +12679,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12691,8 +12687,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="2" t="n">
-        <v>0</v>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12701,39 +12699,41 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12756,38 +12756,38 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12799,12 +12799,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12840,9 +12840,9 @@
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12872,14 +12872,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12911,24 +12911,24 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12945,14 +12945,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -12984,11 +12984,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13018,14 +13018,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13057,11 +13057,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 17,6%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13091,14 +13091,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13130,11 +13130,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13164,14 +13164,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13203,11 +13203,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13237,14 +13237,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13276,11 +13276,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13310,14 +13310,14 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
           <t>UTD-016-PT</t>
@@ -13349,11 +13349,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13380,8 +13380,154 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
+++ b/saida_skus/SKU_UTD-016-PT-ESCORREDOR-DUPLO-DESMONTAVEL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 527,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 36,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▲ 527,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 77,8%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1624,20 +1624,20 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 36,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1762,20 +1762,20 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1914,22 +1914,22 @@
       <c r="I20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2057,51 +2057,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 77,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2135,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,59 +2195,55 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2285,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2357,51 +2349,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2429,17 +2417,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2507,10 +2495,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2519,39 +2505,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2576,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2585,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2619,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2696,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2735,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2846,12 +2830,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2885,11 +2869,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2919,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2996,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3035,11 +3019,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3069,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3146,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3176,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3184,51 +3168,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,8%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3300,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3330,7 +3310,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3338,51 +3318,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3454,12 +3430,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3484,7 +3460,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3492,51 +3468,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3608,12 +3580,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3638,7 +3610,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3646,10 +3618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3658,39 +3628,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3762,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,12 +3807,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3916,12 +3884,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3993,12 +3961,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4070,12 +4038,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4147,12 +4115,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4224,12 +4192,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4301,12 +4269,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4378,12 +4346,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4408,7 +4376,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4416,8 +4384,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4426,37 +4396,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4481,7 +4453,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4489,8 +4461,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4499,37 +4473,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4554,7 +4530,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4562,47 +4538,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4627,7 +4607,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4635,47 +4615,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4700,7 +4684,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4708,8 +4692,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>5</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4718,37 +4704,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4773,7 +4761,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4781,8 +4769,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>3</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4791,37 +4781,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4893,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4970,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5000,7 +4992,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5008,10 +5000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5020,39 +5010,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5077,7 +5065,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5085,10 +5073,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5097,39 +5083,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5154,7 +5138,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5162,51 +5146,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5231,7 +5211,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5239,51 +5219,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5284,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,10 +5292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5328,39 +5302,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5385,7 +5357,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5393,10 +5365,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5405,39 +5375,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5477,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5586,12 +5554,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5663,12 +5631,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5693,7 +5661,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5701,8 +5669,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5711,37 +5681,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5766,7 +5738,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5774,8 +5746,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5784,37 +5758,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,7 +5815,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5847,47 +5823,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5912,55 +5892,59 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5985,7 +5969,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5993,47 +5977,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6058,7 +6046,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6066,47 +6054,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6131,7 +6123,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6139,47 +6131,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6204,7 +6200,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6212,47 +6208,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6320,12 +6320,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6359,11 +6359,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6431,51 +6431,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6509,11 +6505,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6543,12 +6539,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6573,7 +6569,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6581,51 +6577,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6650,25 +6642,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6676,7 +6668,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6693,12 +6685,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6723,7 +6715,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6731,51 +6723,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6800,7 +6788,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6809,24 +6797,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6843,12 +6831,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6873,7 +6861,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6881,10 +6869,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6893,39 +6879,37 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6959,11 +6943,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6993,12 +6977,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7070,12 +7054,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7109,11 +7093,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 71,4%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7143,12 +7127,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7220,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7255,20 +7239,20 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -7276,7 +7260,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7293,12 +7277,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7370,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7400,7 +7384,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7409,24 +7393,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7443,12 +7427,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7520,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7559,11 +7543,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7593,12 +7577,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7623,7 +7607,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7631,8 +7615,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7641,37 +7627,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7699,17 +7687,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7739,12 +7727,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7816,12 +7804,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7846,7 +7834,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7855,24 +7843,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7889,12 +7877,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7966,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7999,17 +7987,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8039,12 +8027,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8116,12 +8104,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8146,7 +8134,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8155,24 +8143,24 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 900,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8189,12 +8177,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8219,7 +8207,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8227,10 +8215,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8239,39 +8225,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8305,11 +8289,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8339,12 +8323,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8416,12 +8400,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8449,17 +8433,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8489,12 +8473,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8566,12 +8550,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8596,33 +8580,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8639,12 +8623,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8716,12 +8700,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8746,7 +8730,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 80,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8755,24 +8739,24 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 900,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8789,12 +8773,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8866,12 +8850,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8905,11 +8889,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8939,12 +8923,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9016,12 +9000,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9049,17 +9033,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9089,12 +9073,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9166,12 +9150,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9196,7 +9180,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9205,24 +9189,24 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9239,12 +9223,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9269,7 +9253,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9277,8 +9261,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9287,37 +9273,39 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9351,11 +9339,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 116,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9385,12 +9373,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9415,7 +9403,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9423,47 +9411,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9497,11 +9489,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9531,12 +9523,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9561,7 +9553,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9569,8 +9561,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>1</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9579,37 +9573,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9643,11 +9639,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,6%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9677,12 +9673,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9754,12 +9750,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9793,11 +9789,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9827,12 +9823,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9857,7 +9853,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9865,10 +9861,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9877,39 +9871,37 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9943,11 +9935,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 116,7%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9977,12 +9969,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10007,7 +9999,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10015,51 +10007,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10093,11 +10081,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10127,12 +10115,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10157,7 +10145,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10165,10 +10153,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10177,39 +10163,37 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10243,11 +10227,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10277,12 +10261,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10354,12 +10338,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10393,11 +10377,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10427,12 +10411,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10504,12 +10488,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10543,11 +10527,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10565,7 +10549,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10577,12 +10561,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10654,12 +10638,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10693,11 +10677,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10727,12 +10711,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10804,12 +10788,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10843,11 +10827,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10877,12 +10861,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10954,12 +10938,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10993,11 +10977,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11027,12 +11011,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11104,12 +11088,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11143,11 +11127,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11165,7 +11149,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -11177,12 +11161,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11207,7 +11191,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11215,8 +11199,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>0</v>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11225,37 +11211,39 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11289,11 +11277,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11323,12 +11311,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11353,7 +11341,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11361,47 +11349,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11435,11 +11427,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11469,12 +11461,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11499,7 +11491,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11507,8 +11499,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="n">
-        <v>1</v>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11517,37 +11511,39 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11581,11 +11577,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11615,12 +11611,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11645,7 +11641,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11653,47 +11649,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11727,11 +11727,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11794,17 +11794,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11873,11 +11873,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11937,33 +11937,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11980,12 +11980,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12019,11 +12019,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12101,15 +12101,15 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12159,17 +12159,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12237,51 +12237,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12306,7 +12302,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 52,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12315,24 +12311,24 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12349,12 +12345,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12379,59 +12375,55 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12465,11 +12457,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12499,12 +12491,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12529,59 +12521,55 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12615,11 +12603,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12637,7 +12625,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12649,12 +12637,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12679,7 +12667,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12687,10 +12675,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12699,39 +12685,37 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12765,11 +12749,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12787,7 +12771,7 @@
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
@@ -12799,12 +12783,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12829,7 +12813,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12837,8 +12821,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="2" t="n">
-        <v>0</v>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -12847,37 +12833,39 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12902,7 +12890,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 46,00</t>
+          <t>R$ 52,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12911,16 +12899,16 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L167" s="2" t="n">
@@ -12928,7 +12916,7 @@
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -12945,12 +12933,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12975,7 +12963,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -12983,47 +12971,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13057,11 +13049,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,6%</t>
+        <v>4</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13091,12 +13083,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13121,7 +13113,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -13129,8 +13121,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" s="2" t="n">
-        <v>1</v>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -13139,37 +13133,39 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13203,11 +13199,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13225,7 +13221,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -13237,12 +13233,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13267,7 +13263,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13275,47 +13271,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13343,17 +13343,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 31,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -13383,12 +13383,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -13456,78 +13456,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,6%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4302299203</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 51,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 31,2%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-016-PT</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor Duplo Desmontavel</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>5482109252</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 49,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-016-PT</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor Duplo Desmontavel</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4302299203</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>R$ 51,90</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>